--- a/artfynd/A 33974-2024 artfynd.xlsx
+++ b/artfynd/A 33974-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,6 +887,138 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120122319</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Spångmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>768524</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7084565</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33974-2024 artfynd.xlsx
+++ b/artfynd/A 33974-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>119719071</v>
       </c>
       <c r="B3" t="n">
-        <v>90527</v>
+        <v>90545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>120122319</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 33974-2024 artfynd.xlsx
+++ b/artfynd/A 33974-2024 artfynd.xlsx
@@ -892,11 +892,11 @@
         <v>120122319</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/artfynd/A 33974-2024 artfynd.xlsx
+++ b/artfynd/A 33974-2024 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>120122319</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 33974-2024 artfynd.xlsx
+++ b/artfynd/A 33974-2024 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>120122319</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 33974-2024 artfynd.xlsx
+++ b/artfynd/A 33974-2024 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>123622700</v>
       </c>
       <c r="B5" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 33974-2024 artfynd.xlsx
+++ b/artfynd/A 33974-2024 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>123622700</v>
       </c>
       <c r="B5" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 33974-2024 artfynd.xlsx
+++ b/artfynd/A 33974-2024 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>123622700</v>
       </c>
       <c r="B5" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 33974-2024 artfynd.xlsx
+++ b/artfynd/A 33974-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1140,6 +1140,108 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133851006</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91916</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skogen, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>768572</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7084550</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-65</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33974-2024 artfynd.xlsx
+++ b/artfynd/A 33974-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1140,108 +1140,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>133851006</v>
-      </c>
-      <c r="B6" t="n">
-        <v>91916</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Skogen, Vb</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>768572</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7084550</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-65</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33974-2024 artfynd.xlsx
+++ b/artfynd/A 33974-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103446576</v>
+        <v>119719071</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>skog V Spångmyran, Ultervik, Vb</t>
+          <t>Degersjön S, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>768572.3183836404</v>
+        <v>768546</v>
       </c>
       <c r="R2" t="n">
-        <v>7084605.054325072</v>
+        <v>7084518</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,62 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119719071</v>
+        <v>103446576</v>
       </c>
       <c r="B3" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Degersjön S, Vb</t>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768546</v>
+        <v>768572</v>
       </c>
       <c r="R3" t="n">
-        <v>7084518</v>
+        <v>7084605</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,85 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120122319</v>
+        <v>122951646</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spångmyran, Vb</t>
+          <t>Spångmyran S Degersjön, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768524</v>
+        <v>768646</v>
       </c>
       <c r="R4" t="n">
-        <v>7084565</v>
+        <v>7084626</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,74 +954,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123622700</v>
+        <v>129792598</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Spångmyran, Spångmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768598</v>
+        <v>768525</v>
       </c>
       <c r="R5" t="n">
-        <v>7084571</v>
+        <v>7084624</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,22 +1036,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre spår spillkråka</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,15 +1071,365 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120122319</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Spångmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>768524</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7084565</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119039845</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>768539</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7084469</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>död gran</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Andreas Garpebring</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123622700</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>V Spångmyran, Ultervik, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>768598</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7084571</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
         <is>
           <t>Andreas Garpebring</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33974-2024 artfynd.xlsx
+++ b/artfynd/A 33974-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129792598</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120122319</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119039845</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719071</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103446576</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122951646</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1430,8 +1465,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123622700</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>